--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_tarapaca.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:31</t>
+    <t xml:space="preserve">2026-09-24 01:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -634,7 +634,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -674,7 +674,7 @@
         <v>0.41</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0.31</v>
@@ -700,7 +700,7 @@
         <v>0.12</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="9">
@@ -827,10 +827,10 @@
         <v>0.23</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="15">
@@ -850,10 +850,10 @@
         <v>0.75</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="16">
@@ -873,10 +873,10 @@
         <v>-0.6</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="17">
@@ -896,10 +896,10 @@
         <v>-0.6</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="18">
@@ -984,10 +984,10 @@
         <v>0.28</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.13</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.37</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="22">
@@ -1007,10 +1007,10 @@
         <v>0.2</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="23">
@@ -1194,7 +1194,7 @@
         <v>-0.56</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.08</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>-0.48</v>
@@ -1301,10 +1301,10 @@
         <v>0.53</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="37">
@@ -1324,10 +1324,10 @@
         <v>0.39</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="38">
@@ -1347,10 +1347,10 @@
         <v>-0.15</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="39">
@@ -1458,10 +1458,10 @@
         <v>-0.22</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="44">
@@ -1481,10 +1481,10 @@
         <v>0.35</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="45">
@@ -1932,10 +1932,10 @@
         <v>0.3</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.07</v>
+        <v>-0.12</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="66">
@@ -1955,10 +1955,10 @@
         <v>-0.39</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="67">
@@ -1981,7 +1981,7 @@
         <v>0.18</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_tarapaca.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:21</t>
+    <t xml:space="preserve">2026-10-01 23:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2021_tarapaca.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:22</t>
+    <t xml:space="preserve">2026-10-05 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
